--- a/assets/files/templates/SafePlum_hot_work_permit.xlsx
+++ b/assets/files/templates/SafePlum_hot_work_permit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="89">
   <si>
     <t xml:space="preserve">화기작업 허가서 — 작성 안내</t>
   </si>
@@ -3124,9 +3124,6 @@
     <t xml:space="preserve">조치</t>
   </si>
   <si>
-    <t xml:space="preserve">12:50</t>
-  </si>
-  <si>
     <t xml:space="preserve">배관 랙 하부</t>
   </si>
   <si>
@@ -3186,9 +3183,6 @@
     <t xml:space="preserve">종료 시각</t>
   </si>
   <si>
-    <t xml:space="preserve">15:40</t>
-  </si>
-  <si>
     <t xml:space="preserve">잔불 확인 시각</t>
   </si>
   <si>
@@ -3421,12 +3415,6 @@
   </si>
   <si>
     <t xml:space="preserve">허가자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:00</t>
   </si>
   <si>
     <r>
@@ -3464,8 +3452,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -3747,7 +3735,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3836,11 +3824,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3852,7 +3844,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3864,19 +3856,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4625,100 +4617,100 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="22" t="n">
+        <v>0.534722222222222</v>
+      </c>
+      <c r="B30" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="C30" s="23"/>
+      <c r="D30" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="22" t="s">
+      <c r="E30" s="24"/>
+      <c r="F30" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22" t="s">
+      <c r="G30" s="24"/>
+      <c r="H30" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="G30" s="22"/>
-      <c r="H30" s="23" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+    </row>
+    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-    </row>
-    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-    </row>
-    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>0.652777777777778</v>
+      </c>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="F35" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>75</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F36" s="18"/>
       <c r="G36" s="18"/>
       <c r="H36" s="18"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
+      <c r="A38" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="58">
@@ -4831,7 +4823,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4843,7 +4835,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -4854,20 +4846,20 @@
       <c r="H2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>83</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>85</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>22</v>
@@ -4882,631 +4874,631 @@
         <v>6</v>
       </c>
       <c r="J4" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>0.652777777777778</v>
+      </c>
+      <c r="E5" s="31" t="s">
         <v>86</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>90</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>69</v>
+        <v>88</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>68</v>
       </c>
       <c r="J5" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="22" t="s">
-        <v>69</v>
+      <c r="K5" s="24" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="n">
+      <c r="A6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="n">
+      <c r="A8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="n">
+      <c r="A10" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="n">
+      <c r="A12" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="n">
+      <c r="A21" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="n">
+      <c r="A22" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="n">
+      <c r="A24" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="n">
+      <c r="A25" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="n">
+      <c r="A26" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="n">
+      <c r="A27" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="n">
+      <c r="A28" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="n">
+      <c r="A29" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="n">
+      <c r="A30" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="n">
+      <c r="A31" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="n">
+      <c r="A32" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="n">
+      <c r="A33" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24" t="n">
+      <c r="A34" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24" t="n">
+      <c r="A35" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="n">
+      <c r="A36" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24" t="n">
+      <c r="A37" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24" t="n">
+      <c r="A38" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="n">
+      <c r="A39" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="24" t="n">
+      <c r="A40" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24" t="n">
+      <c r="A41" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="24" t="n">
+      <c r="A42" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="24" t="n">
+      <c r="A43" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="24" t="n">
+      <c r="A44" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/assets/files/templates/SafePlum_hot_work_permit.xlsx
+++ b/assets/files/templates/SafePlum_hot_work_permit.xlsx
@@ -4179,12 +4179,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -4197,12 +4197,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
@@ -4215,12 +4215,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
